--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -50,8 +50,8 @@
     <sheet name="Morgan Park" sheetId="41" r:id="rId41"/>
     <sheet name="Near South Side" sheetId="42" r:id="rId42"/>
     <sheet name="Mckinley Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Garfield Park" sheetId="44" r:id="rId44"/>
-    <sheet name="Rogers Park" sheetId="45" r:id="rId45"/>
+    <sheet name="Rogers Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Garfield Park" sheetId="45" r:id="rId45"/>
     <sheet name="Brighton Park" sheetId="46" r:id="rId46"/>
     <sheet name="West Elsdon" sheetId="47" r:id="rId47"/>
     <sheet name="Hyde Park" sheetId="48" r:id="rId48"/>
@@ -16776,40 +16776,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>176</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>203</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>179</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>191</v>
+        <v>47</v>
       </c>
       <c r="H2">
-        <v>214</v>
+        <v>52</v>
       </c>
       <c r="I2">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="J2">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="K2">
-        <v>233</v>
+        <v>69</v>
       </c>
       <c r="L2">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="M2">
-        <v>178</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16817,40 +16817,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>274</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>367</v>
+        <v>52</v>
       </c>
       <c r="D3">
-        <v>354</v>
+        <v>46</v>
       </c>
       <c r="E3">
-        <v>389</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>404</v>
+        <v>45</v>
       </c>
       <c r="G3">
-        <v>406</v>
+        <v>48</v>
       </c>
       <c r="H3">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="I3">
-        <v>322</v>
+        <v>64</v>
       </c>
       <c r="J3">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="K3">
-        <v>318</v>
+        <v>54</v>
       </c>
       <c r="L3">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="M3">
-        <v>261</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16858,37 +16858,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K4">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L4">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="M4">
         <v>32</v>
@@ -16899,40 +16899,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16940,40 +16940,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>376</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>405</v>
+        <v>122</v>
       </c>
       <c r="D6">
-        <v>395</v>
+        <v>103</v>
       </c>
       <c r="E6">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="G6">
-        <v>372</v>
+        <v>89</v>
       </c>
       <c r="H6">
-        <v>253</v>
+        <v>112</v>
       </c>
       <c r="I6">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>328</v>
+        <v>73</v>
       </c>
       <c r="K6">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="L6">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="M6">
-        <v>156</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -16981,40 +16981,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>872</v>
+        <v>173</v>
       </c>
       <c r="C7">
-        <v>1036</v>
+        <v>249</v>
       </c>
       <c r="D7">
-        <v>1024</v>
+        <v>219</v>
       </c>
       <c r="E7">
-        <v>1103</v>
+        <v>206</v>
       </c>
       <c r="F7">
-        <v>993</v>
+        <v>204</v>
       </c>
       <c r="G7">
-        <v>1055</v>
+        <v>221</v>
       </c>
       <c r="H7">
-        <v>971</v>
+        <v>249</v>
       </c>
       <c r="I7">
-        <v>851</v>
+        <v>261</v>
       </c>
       <c r="J7">
-        <v>958</v>
+        <v>259</v>
       </c>
       <c r="K7">
-        <v>875</v>
+        <v>229</v>
       </c>
       <c r="L7">
-        <v>750</v>
+        <v>210</v>
       </c>
       <c r="M7">
-        <v>658</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -17088,40 +17088,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="C2">
-        <v>45</v>
+        <v>176</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="G2">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="H2">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="I2">
-        <v>61</v>
+        <v>192</v>
       </c>
       <c r="J2">
-        <v>71</v>
+        <v>234</v>
       </c>
       <c r="K2">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="L2">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="M2">
-        <v>52</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17129,40 +17129,40 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>55</v>
+        <v>274</v>
       </c>
       <c r="C3">
-        <v>52</v>
+        <v>367</v>
       </c>
       <c r="D3">
-        <v>46</v>
+        <v>354</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>389</v>
       </c>
       <c r="F3">
-        <v>45</v>
+        <v>404</v>
       </c>
       <c r="G3">
-        <v>48</v>
+        <v>406</v>
       </c>
       <c r="H3">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="I3">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="J3">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="K3">
-        <v>54</v>
+        <v>318</v>
       </c>
       <c r="L3">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="M3">
-        <v>69</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17170,37 +17170,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L4">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="M4">
         <v>32</v>
@@ -17211,40 +17211,40 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17252,40 +17252,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>63</v>
+        <v>376</v>
       </c>
       <c r="C6">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D6">
-        <v>103</v>
+        <v>395</v>
       </c>
       <c r="E6">
-        <v>105</v>
+        <v>429</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>372</v>
       </c>
       <c r="H6">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="I6">
-        <v>95</v>
+        <v>262</v>
       </c>
       <c r="J6">
-        <v>73</v>
+        <v>328</v>
       </c>
       <c r="K6">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="L6">
-        <v>63</v>
+        <v>224</v>
       </c>
       <c r="M6">
-        <v>44</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17293,40 +17293,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>173</v>
+        <v>872</v>
       </c>
       <c r="C7">
-        <v>249</v>
+        <v>1036</v>
       </c>
       <c r="D7">
-        <v>219</v>
+        <v>1024</v>
       </c>
       <c r="E7">
-        <v>206</v>
+        <v>1103</v>
       </c>
       <c r="F7">
-        <v>204</v>
+        <v>993</v>
       </c>
       <c r="G7">
-        <v>221</v>
+        <v>1055</v>
       </c>
       <c r="H7">
-        <v>249</v>
+        <v>971</v>
       </c>
       <c r="I7">
-        <v>261</v>
+        <v>851</v>
       </c>
       <c r="J7">
-        <v>259</v>
+        <v>958</v>
       </c>
       <c r="K7">
-        <v>229</v>
+        <v>875</v>
       </c>
       <c r="L7">
-        <v>210</v>
+        <v>750</v>
       </c>
       <c r="M7">
-        <v>199</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/output/violent-crime-ytd.xlsx
+++ b/output/violent-crime-ytd.xlsx
@@ -901,7 +901,7 @@
         <v>5381</v>
       </c>
       <c r="M2">
-        <v>5137</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -942,7 +942,7 @@
         <v>5828</v>
       </c>
       <c r="M3">
-        <v>5759</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -968,7 +968,7 @@
         <v>1336</v>
       </c>
       <c r="H4">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="I4">
         <v>1627</v>
@@ -983,7 +983,7 @@
         <v>1582</v>
       </c>
       <c r="M4">
-        <v>1567</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1065,7 +1065,7 @@
         <v>4787</v>
       </c>
       <c r="M6">
-        <v>3752</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>20011</v>
       </c>
       <c r="H7">
-        <v>20568</v>
+        <v>20569</v>
       </c>
       <c r="I7">
         <v>20825</v>
@@ -1106,7 +1106,7 @@
         <v>17937</v>
       </c>
       <c r="M7">
-        <v>16559</v>
+        <v>16612</v>
       </c>
     </row>
   </sheetData>
@@ -2133,7 +2133,7 @@
         <v>59</v>
       </c>
       <c r="M3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2297,7 +2297,7 @@
         <v>202</v>
       </c>
       <c r="M7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2404,7 @@
         <v>298</v>
       </c>
       <c r="M2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2609,7 +2609,7 @@
         <v>997</v>
       </c>
       <c r="M7">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +3028,7 @@
         <v>201</v>
       </c>
       <c r="M2">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3069,7 +3069,7 @@
         <v>233</v>
       </c>
       <c r="M3">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3233,7 +3233,7 @@
         <v>665</v>
       </c>
       <c r="M7">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -3381,7 +3381,7 @@
         <v>106</v>
       </c>
       <c r="M3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -3545,7 +3545,7 @@
         <v>236</v>
       </c>
       <c r="M7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4543,7 +4543,7 @@
         <v>144</v>
       </c>
       <c r="M2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4748,7 +4748,7 @@
         <v>569</v>
       </c>
       <c r="M7">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4789,7 +4789,7 @@
         <v>1163</v>
       </c>
       <c r="M8">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4871,7 +4871,7 @@
         <v>118</v>
       </c>
       <c r="M10">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4912,7 +4912,7 @@
         <v>288</v>
       </c>
       <c r="M11">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4953,7 +4953,7 @@
         <v>40</v>
       </c>
       <c r="M12">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5035,7 +5035,7 @@
         <v>88</v>
       </c>
       <c r="M14">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5240,7 +5240,7 @@
         <v>477</v>
       </c>
       <c r="M19">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5281,7 +5281,7 @@
         <v>435</v>
       </c>
       <c r="M20">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5445,7 +5445,7 @@
         <v>46</v>
       </c>
       <c r="M24">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5650,7 +5650,7 @@
         <v>997</v>
       </c>
       <c r="M29">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5978,7 +5978,7 @@
         <v>665</v>
       </c>
       <c r="M37">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6470,7 +6470,7 @@
         <v>88</v>
       </c>
       <c r="M49">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6552,7 +6552,7 @@
         <v>226</v>
       </c>
       <c r="M51">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6593,7 +6593,7 @@
         <v>356</v>
       </c>
       <c r="M52">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6716,7 +6716,7 @@
         <v>184</v>
       </c>
       <c r="M55">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6921,7 +6921,7 @@
         <v>113</v>
       </c>
       <c r="M60">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -7029,7 +7029,7 @@
         <v>326</v>
       </c>
       <c r="H63">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I63">
         <v>344</v>
@@ -7044,7 +7044,7 @@
         <v>351</v>
       </c>
       <c r="M63">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -7126,7 +7126,7 @@
         <v>342</v>
       </c>
       <c r="M65">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -7167,7 +7167,7 @@
         <v>49</v>
       </c>
       <c r="M66">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -7208,7 +7208,7 @@
         <v>603</v>
       </c>
       <c r="M67">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -7454,7 +7454,7 @@
         <v>143</v>
       </c>
       <c r="M73">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7577,7 +7577,7 @@
         <v>275</v>
       </c>
       <c r="M76">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7618,7 +7618,7 @@
         <v>116</v>
       </c>
       <c r="M77">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7741,7 +7741,7 @@
         <v>56</v>
       </c>
       <c r="M80">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7864,7 +7864,7 @@
         <v>391</v>
       </c>
       <c r="M83">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7946,7 +7946,7 @@
         <v>883</v>
       </c>
       <c r="M85">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7987,7 +7987,7 @@
         <v>122</v>
       </c>
       <c r="M86">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -8069,7 +8069,7 @@
         <v>190</v>
       </c>
       <c r="M88">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -8151,7 +8151,7 @@
         <v>183</v>
       </c>
       <c r="M90">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -8192,7 +8192,7 @@
         <v>236</v>
       </c>
       <c r="M91">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -8274,7 +8274,7 @@
         <v>86</v>
       </c>
       <c r="M93">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -8315,7 +8315,7 @@
         <v>214</v>
       </c>
       <c r="M94">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -8397,7 +8397,7 @@
         <v>202</v>
       </c>
       <c r="M96">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -8520,7 +8520,7 @@
         <v>309</v>
       </c>
       <c r="M99">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -8587,7 +8587,7 @@
         <v>20011</v>
       </c>
       <c r="H101">
-        <v>20568</v>
+        <v>20569</v>
       </c>
       <c r="I101">
         <v>20825</v>
@@ -8602,7 +8602,7 @@
         <v>17937</v>
       </c>
       <c r="M101">
-        <v>16559</v>
+        <v>16612</v>
       </c>
     </row>
   </sheetData>
@@ -8852,7 +8852,7 @@
         <v>60</v>
       </c>
       <c r="M3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8975,7 +8975,7 @@
         <v>51</v>
       </c>
       <c r="M6">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9016,7 +9016,7 @@
         <v>184</v>
       </c>
       <c r="M7">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -9205,7 +9205,7 @@
         <v>40</v>
       </c>
       <c r="M4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9328,7 +9328,7 @@
         <v>603</v>
       </c>
       <c r="M7">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -9476,7 +9476,7 @@
         <v>142</v>
       </c>
       <c r="M3">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9517,7 +9517,7 @@
         <v>39</v>
       </c>
       <c r="M4">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9640,7 +9640,7 @@
         <v>435</v>
       </c>
       <c r="M7">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -9788,7 +9788,7 @@
         <v>158</v>
       </c>
       <c r="M3">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9952,7 +9952,7 @@
         <v>391</v>
       </c>
       <c r="M7">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -10059,7 +10059,7 @@
         <v>110</v>
       </c>
       <c r="M2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10100,7 +10100,7 @@
         <v>85</v>
       </c>
       <c r="M3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -10141,7 +10141,7 @@
         <v>19</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10264,7 +10264,7 @@
         <v>288</v>
       </c>
       <c r="M7">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -12365,7 +12365,7 @@
         <v>86</v>
       </c>
       <c r="M6">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -12406,7 +12406,7 @@
         <v>342</v>
       </c>
       <c r="M7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -12786,7 +12786,7 @@
         <v>196</v>
       </c>
       <c r="M2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -12827,7 +12827,7 @@
         <v>186</v>
       </c>
       <c r="M3">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -12991,7 +12991,7 @@
         <v>569</v>
       </c>
       <c r="M7">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -13571,7 +13571,7 @@
         <v>123</v>
       </c>
       <c r="M6">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13612,7 +13612,7 @@
         <v>275</v>
       </c>
       <c r="M7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -14025,7 +14025,7 @@
         <v>168</v>
       </c>
       <c r="M2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14230,7 +14230,7 @@
         <v>477</v>
       </c>
       <c r="M7">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -14337,7 +14337,7 @@
         <v>87</v>
       </c>
       <c r="M2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -14378,7 +14378,7 @@
         <v>126</v>
       </c>
       <c r="M3">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14501,7 +14501,7 @@
         <v>69</v>
       </c>
       <c r="M6">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14542,7 +14542,7 @@
         <v>309</v>
       </c>
       <c r="M7">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -14690,7 +14690,7 @@
         <v>38</v>
       </c>
       <c r="M3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14854,7 +14854,7 @@
         <v>116</v>
       </c>
       <c r="M7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -14961,7 +14961,7 @@
         <v>30</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15148,7 +15148,7 @@
         <v>88</v>
       </c>
       <c r="M7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -16493,7 +16493,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -16633,7 +16633,7 @@
         <v>40</v>
       </c>
       <c r="M7">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -16740,7 +16740,7 @@
         <v>70</v>
       </c>
       <c r="M2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16945,7 +16945,7 @@
         <v>226</v>
       </c>
       <c r="M7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -17093,7 +17093,7 @@
         <v>408</v>
       </c>
       <c r="M3">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -17134,7 +17134,7 @@
         <v>85</v>
       </c>
       <c r="M4">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17216,7 +17216,7 @@
         <v>293</v>
       </c>
       <c r="M6">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -17257,7 +17257,7 @@
         <v>1163</v>
       </c>
       <c r="M7">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -17725,7 +17725,7 @@
         <v>27</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17842,7 +17842,7 @@
         <v>214</v>
       </c>
       <c r="M7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -19246,7 +19246,7 @@
         <v>66</v>
       </c>
       <c r="M4">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -19345,7 +19345,7 @@
         <v>122</v>
       </c>
       <c r="M7">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -19755,7 +19755,7 @@
         <v>52</v>
       </c>
       <c r="M2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19948,7 +19948,7 @@
         <v>143</v>
       </c>
       <c r="M7">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -21578,7 +21578,7 @@
         <v>50</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -21742,7 +21742,7 @@
         <v>144</v>
       </c>
       <c r="M7">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -21849,7 +21849,7 @@
         <v>58</v>
       </c>
       <c r="M2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -21890,7 +21890,7 @@
         <v>65</v>
       </c>
       <c r="M3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -22054,7 +22054,7 @@
         <v>190</v>
       </c>
       <c r="M7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -22625,7 +22625,7 @@
         <v>26</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -22666,7 +22666,7 @@
         <v>113</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -23082,7 +23082,7 @@
         <v>60</v>
       </c>
       <c r="M2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -23287,7 +23287,7 @@
         <v>183</v>
       </c>
       <c r="M7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -23858,7 +23858,7 @@
         <v>32</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -23899,7 +23899,7 @@
         <v>118</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -24903,7 +24903,7 @@
         <v>46</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -24985,7 +24985,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -25970,7 +25970,7 @@
         <v>27</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -26011,7 +26011,7 @@
         <v>86</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -28429,7 +28429,7 @@
         <v>265</v>
       </c>
       <c r="M2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -28470,7 +28470,7 @@
         <v>363</v>
       </c>
       <c r="M3">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -28634,7 +28634,7 @@
         <v>883</v>
       </c>
       <c r="M7">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -29329,7 +29329,7 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -29525,7 +29525,7 @@
         <v>88</v>
       </c>
       <c r="M7">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -30867,7 +30867,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -30960,7 +30960,7 @@
         <v>49</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -31149,7 +31149,7 @@
         <v>4</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -31254,7 +31254,7 @@
         <v>46</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -31498,7 +31498,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -31539,7 +31539,7 @@
         <v>56</v>
       </c>
       <c r="M7">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -31687,7 +31687,7 @@
         <v>117</v>
       </c>
       <c r="M3">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -31851,7 +31851,7 @@
         <v>356</v>
       </c>
       <c r="M7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
